--- a/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_mapping_params.xlsx
+++ b/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_mapping_params.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="80">
   <si>
     <t>mapping_id</t>
   </si>
@@ -64,6 +64,21 @@
     <t>effective_date</t>
   </si>
   <si>
+    <t>sensor_id</t>
+  </si>
+  <si>
+    <t>qfa_window</t>
+  </si>
+  <si>
+    <t>production_evidence</t>
+  </si>
+  <si>
+    <t>process_floor_threshold</t>
+  </si>
+  <si>
+    <t>response_loss_enabled</t>
+  </si>
+  <si>
     <t>Q_TI_missing_rate</t>
   </si>
   <si>
@@ -88,6 +103,12 @@
     <t>Q_FA_info_empty_cov</t>
   </si>
   <si>
+    <t>Q_FA_DO_1_4_process_floor</t>
+  </si>
+  <si>
+    <t>Q_FA_DO_2_4_process_floor</t>
+  </si>
+  <si>
     <t>Q_TI</t>
   </si>
   <si>
@@ -121,9 +142,15 @@
     <t>info_empty_cov</t>
   </si>
   <si>
+    <t>qfa_unavailable</t>
+  </si>
+  <si>
     <t>piecewise_linear</t>
   </si>
   <si>
+    <t>process_floor_route</t>
+  </si>
+  <si>
     <t>&gt;0.15</t>
   </si>
   <si>
@@ -205,13 +232,28 @@
     <t>d2_mapping.yaml</t>
   </si>
   <si>
-    <t>d2_v1_p0p1</t>
-  </si>
-  <si>
-    <t>NorthBank_D2_v1_20260710</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
+    <t>d2_sensors.yaml+d2_mapping.yaml</t>
+  </si>
+  <si>
+    <t>d2_v1_process_floor_r1</t>
+  </si>
+  <si>
+    <t>NorthBank_D2_v1_20260722</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>DO_1_4</t>
+  </si>
+  <si>
+    <t>DO_2_4</t>
+  </si>
+  <si>
+    <t>6h</t>
+  </si>
+  <si>
+    <t>missing,long_gap,sensor_freeze</t>
   </si>
 </sst>
 </file>
@@ -569,10 +611,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -621,19 +663,34 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E2">
         <v>0.005</v>
@@ -648,42 +705,42 @@
         <v>0.15</v>
       </c>
       <c r="I2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M2" t="s">
+        <v>71</v>
+      </c>
+      <c r="N2" t="s">
+        <v>73</v>
+      </c>
+      <c r="O2" t="s">
+        <v>74</v>
+      </c>
+      <c r="P2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
         <v>43</v>
-      </c>
-      <c r="K2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M2" t="s">
-        <v>62</v>
-      </c>
-      <c r="N2" t="s">
-        <v>63</v>
-      </c>
-      <c r="O2" t="s">
-        <v>64</v>
-      </c>
-      <c r="P2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>35</v>
       </c>
       <c r="E3">
         <v>0.001</v>
@@ -698,42 +755,42 @@
         <v>0.05</v>
       </c>
       <c r="I3" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="J3" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="K3" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L3" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="M3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="N3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="O3" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="P3" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:21">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E4">
         <v>0.001</v>
@@ -748,42 +805,42 @@
         <v>0.05</v>
       </c>
       <c r="I4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K4" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" t="s">
+        <v>66</v>
+      </c>
+      <c r="M4" t="s">
+        <v>71</v>
+      </c>
+      <c r="N4" t="s">
+        <v>73</v>
+      </c>
+      <c r="O4" t="s">
+        <v>74</v>
+      </c>
+      <c r="P4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
         <v>37</v>
       </c>
-      <c r="J4" t="s">
-        <v>44</v>
-      </c>
-      <c r="K4" t="s">
-        <v>51</v>
-      </c>
-      <c r="L4" t="s">
-        <v>57</v>
-      </c>
-      <c r="M4" t="s">
-        <v>62</v>
-      </c>
-      <c r="N4" t="s">
-        <v>63</v>
-      </c>
-      <c r="O4" t="s">
-        <v>64</v>
-      </c>
-      <c r="P4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E5">
         <v>0.005</v>
@@ -798,42 +855,42 @@
         <v>0.1</v>
       </c>
       <c r="I5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" t="s">
+        <v>54</v>
+      </c>
+      <c r="K5" t="s">
+        <v>59</v>
+      </c>
+      <c r="L5" t="s">
+        <v>65</v>
+      </c>
+      <c r="M5" t="s">
+        <v>71</v>
+      </c>
+      <c r="N5" t="s">
+        <v>73</v>
+      </c>
+      <c r="O5" t="s">
+        <v>74</v>
+      </c>
+      <c r="P5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
         <v>38</v>
       </c>
-      <c r="J5" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L5" t="s">
-        <v>56</v>
-      </c>
-      <c r="M5" t="s">
-        <v>62</v>
-      </c>
-      <c r="N5" t="s">
-        <v>63</v>
-      </c>
-      <c r="O5" t="s">
-        <v>64</v>
-      </c>
-      <c r="P5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -848,42 +905,42 @@
         <v>360</v>
       </c>
       <c r="I6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K6" t="s">
+        <v>61</v>
+      </c>
+      <c r="L6" t="s">
+        <v>67</v>
+      </c>
+      <c r="M6" t="s">
+        <v>71</v>
+      </c>
+      <c r="N6" t="s">
+        <v>73</v>
+      </c>
+      <c r="O6" t="s">
+        <v>74</v>
+      </c>
+      <c r="P6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>39</v>
       </c>
-      <c r="J6" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" t="s">
-        <v>52</v>
-      </c>
-      <c r="L6" t="s">
-        <v>58</v>
-      </c>
-      <c r="M6" t="s">
-        <v>62</v>
-      </c>
-      <c r="N6" t="s">
-        <v>63</v>
-      </c>
-      <c r="O6" t="s">
-        <v>64</v>
-      </c>
-      <c r="P6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -898,42 +955,42 @@
         <v>120</v>
       </c>
       <c r="I7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" t="s">
+        <v>62</v>
+      </c>
+      <c r="L7" t="s">
+        <v>68</v>
+      </c>
+      <c r="M7" t="s">
+        <v>71</v>
+      </c>
+      <c r="N7" t="s">
+        <v>73</v>
+      </c>
+      <c r="O7" t="s">
+        <v>74</v>
+      </c>
+      <c r="P7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
         <v>40</v>
       </c>
-      <c r="J7" t="s">
-        <v>47</v>
-      </c>
-      <c r="K7" t="s">
-        <v>53</v>
-      </c>
-      <c r="L7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M7" t="s">
-        <v>62</v>
-      </c>
-      <c r="N7" t="s">
-        <v>63</v>
-      </c>
-      <c r="O7" t="s">
-        <v>64</v>
-      </c>
-      <c r="P7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -948,42 +1005,42 @@
         <v>40</v>
       </c>
       <c r="I8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K8" t="s">
+        <v>63</v>
+      </c>
+      <c r="L8" t="s">
+        <v>69</v>
+      </c>
+      <c r="M8" t="s">
+        <v>71</v>
+      </c>
+      <c r="N8" t="s">
+        <v>73</v>
+      </c>
+      <c r="O8" t="s">
+        <v>74</v>
+      </c>
+      <c r="P8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
         <v>41</v>
       </c>
-      <c r="J8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L8" t="s">
-        <v>60</v>
-      </c>
-      <c r="M8" t="s">
-        <v>62</v>
-      </c>
-      <c r="N8" t="s">
-        <v>63</v>
-      </c>
-      <c r="O8" t="s">
-        <v>64</v>
-      </c>
-      <c r="P8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E9">
         <v>0.02</v>
@@ -998,28 +1055,110 @@
         <v>0.5</v>
       </c>
       <c r="I9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" t="s">
+        <v>58</v>
+      </c>
+      <c r="K9" t="s">
+        <v>64</v>
+      </c>
+      <c r="L9" t="s">
+        <v>70</v>
+      </c>
+      <c r="M9" t="s">
+        <v>71</v>
+      </c>
+      <c r="N9" t="s">
+        <v>73</v>
+      </c>
+      <c r="O9" t="s">
+        <v>74</v>
+      </c>
+      <c r="P9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
         <v>42</v>
       </c>
-      <c r="J9" t="s">
-        <v>49</v>
-      </c>
-      <c r="K9" t="s">
-        <v>55</v>
-      </c>
-      <c r="L9" t="s">
-        <v>61</v>
-      </c>
-      <c r="M9" t="s">
-        <v>62</v>
-      </c>
-      <c r="N9" t="s">
-        <v>63</v>
-      </c>
-      <c r="O9" t="s">
-        <v>64</v>
-      </c>
-      <c r="P9" t="s">
-        <v>65</v>
+      <c r="D10" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10" t="s">
+        <v>72</v>
+      </c>
+      <c r="N10" t="s">
+        <v>73</v>
+      </c>
+      <c r="O10" t="s">
+        <v>74</v>
+      </c>
+      <c r="P10" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>76</v>
+      </c>
+      <c r="R10" t="s">
+        <v>78</v>
+      </c>
+      <c r="S10" t="s">
+        <v>79</v>
+      </c>
+      <c r="T10">
+        <v>0.2</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M11" t="s">
+        <v>72</v>
+      </c>
+      <c r="N11" t="s">
+        <v>73</v>
+      </c>
+      <c r="O11" t="s">
+        <v>74</v>
+      </c>
+      <c r="P11" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>77</v>
+      </c>
+      <c r="R11" t="s">
+        <v>78</v>
+      </c>
+      <c r="S11" t="s">
+        <v>79</v>
+      </c>
+      <c r="T11">
+        <v>0.2</v>
+      </c>
+      <c r="U11" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_mapping_params.xlsx
+++ b/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_mapping_params.xlsx
@@ -235,13 +235,13 @@
     <t>d2_sensors.yaml+d2_mapping.yaml</t>
   </si>
   <si>
-    <t>d2_v1_process_floor_r1</t>
-  </si>
-  <si>
-    <t>NorthBank_D2_v1_20260722</t>
-  </si>
-  <si>
-    <t>2026-07-22</t>
+    <t>d2_v2_hard_availability_r1</t>
+  </si>
+  <si>
+    <t>NorthBank_D2_v2_20260804</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
   </si>
   <si>
     <t>DO_1_4</t>
@@ -253,7 +253,7 @@
     <t>6h</t>
   </si>
   <si>
-    <t>missing,long_gap,sensor_freeze</t>
+    <t>missing,long_gap,hard_observed_stasis</t>
   </si>
 </sst>
 </file>

--- a/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_mapping_params.xlsx
+++ b/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_mapping_params.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="89">
   <si>
     <t>mapping_id</t>
   </si>
@@ -40,6 +40,12 @@
     <t>break_4</t>
   </si>
   <si>
+    <t>break_5</t>
+  </si>
+  <si>
+    <t>score_zone_1</t>
+  </si>
+  <si>
     <t>score_zone_1_to_2</t>
   </si>
   <si>
@@ -85,10 +91,10 @@
     <t>Q_TI_duplicate_rate</t>
   </si>
   <si>
-    <t>Q_TI_out_of_order</t>
-  </si>
-  <si>
-    <t>Q_TI_irregular_rate</t>
+    <t>Q_TI_out_of_order_rate</t>
+  </si>
+  <si>
+    <t>Q_TI_true_irregular_rate</t>
   </si>
   <si>
     <t>Q_GS_L_max_min</t>
@@ -124,10 +130,10 @@
     <t>duplicate_rate</t>
   </si>
   <si>
-    <t>out_of_order</t>
-  </si>
-  <si>
-    <t>irregular_rate</t>
+    <t>out_of_order_rate</t>
+  </si>
+  <si>
+    <t>true_irregular_rate</t>
   </si>
   <si>
     <t>L_max_min</t>
@@ -151,25 +157,46 @@
     <t>process_floor_route</t>
   </si>
   <si>
+    <t>&gt;0.25</t>
+  </si>
+  <si>
+    <t>&gt;0.09</t>
+  </si>
+  <si>
     <t>&gt;0.15</t>
   </si>
   <si>
-    <t>&gt;0.05</t>
-  </si>
-  <si>
-    <t>&gt;0.1</t>
-  </si>
-  <si>
-    <t>&gt;360</t>
-  </si>
-  <si>
-    <t>&gt;120</t>
-  </si>
-  <si>
-    <t>&gt;40</t>
-  </si>
-  <si>
-    <t>&gt;0.5</t>
+    <t>&gt;660</t>
+  </si>
+  <si>
+    <t>&gt;210</t>
+  </si>
+  <si>
+    <t>&gt;65</t>
+  </si>
+  <si>
+    <t>&gt;0.8</t>
+  </si>
+  <si>
+    <t>0.15-0.25</t>
+  </si>
+  <si>
+    <t>0.05-0.09</t>
+  </si>
+  <si>
+    <t>0.1-0.15</t>
+  </si>
+  <si>
+    <t>360-660</t>
+  </si>
+  <si>
+    <t>120-210</t>
+  </si>
+  <si>
+    <t>40-65</t>
+  </si>
+  <si>
+    <t>0.5-0.8</t>
   </si>
   <si>
     <t>0.05-0.15</t>
@@ -235,10 +262,10 @@
     <t>d2_sensors.yaml+d2_mapping.yaml</t>
   </si>
   <si>
-    <t>d2_v2_hard_availability_r1</t>
-  </si>
-  <si>
-    <t>NorthBank_D2_v2_20260804</t>
+    <t>d2_v3_source_timestamp_qti_r1</t>
+  </si>
+  <si>
+    <t>NorthBank_D2_v3_20260804</t>
   </si>
   <si>
     <t>2026-08-04</t>
@@ -611,10 +638,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -678,19 +705,25 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:23">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E2">
         <v>0.005</v>
@@ -704,43 +737,49 @@
       <c r="H2">
         <v>0.15</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2">
+        <v>0.25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M2" t="s">
+        <v>68</v>
+      </c>
+      <c r="N2" t="s">
+        <v>74</v>
+      </c>
+      <c r="O2" t="s">
+        <v>80</v>
+      </c>
+      <c r="P2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>83</v>
+      </c>
+      <c r="R2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" t="s">
         <v>45</v>
-      </c>
-      <c r="J2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K2" t="s">
-        <v>59</v>
-      </c>
-      <c r="L2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M2" t="s">
-        <v>71</v>
-      </c>
-      <c r="N2" t="s">
-        <v>73</v>
-      </c>
-      <c r="O2" t="s">
-        <v>74</v>
-      </c>
-      <c r="P2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s">
-        <v>43</v>
       </c>
       <c r="E3">
         <v>0.001</v>
@@ -754,43 +793,49 @@
       <c r="H3">
         <v>0.05</v>
       </c>
-      <c r="I3" t="s">
-        <v>46</v>
+      <c r="I3">
+        <v>0.09</v>
       </c>
       <c r="J3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="K3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="L3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="M3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P3" t="s">
-        <v>75</v>
+        <v>82</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>83</v>
+      </c>
+      <c r="R3" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:23">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E4">
         <v>0.001</v>
@@ -804,43 +849,49 @@
       <c r="H4">
         <v>0.05</v>
       </c>
-      <c r="I4" t="s">
-        <v>46</v>
+      <c r="I4">
+        <v>0.09</v>
       </c>
       <c r="J4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="K4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="L4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="M4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P4" t="s">
-        <v>75</v>
+        <v>82</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>83</v>
+      </c>
+      <c r="R4" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:23">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E5">
         <v>0.005</v>
@@ -854,43 +905,49 @@
       <c r="H5">
         <v>0.1</v>
       </c>
-      <c r="I5" t="s">
-        <v>47</v>
+      <c r="I5">
+        <v>0.15</v>
       </c>
       <c r="J5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="K5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P5" t="s">
-        <v>75</v>
+        <v>82</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>83</v>
+      </c>
+      <c r="R5" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:23">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -904,43 +961,49 @@
       <c r="H6">
         <v>360</v>
       </c>
-      <c r="I6" t="s">
-        <v>48</v>
+      <c r="I6">
+        <v>660</v>
       </c>
       <c r="J6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="K6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="M6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="O6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P6" t="s">
-        <v>75</v>
+        <v>82</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>83</v>
+      </c>
+      <c r="R6" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:23">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -954,43 +1017,49 @@
       <c r="H7">
         <v>120</v>
       </c>
-      <c r="I7" t="s">
-        <v>49</v>
+      <c r="I7">
+        <v>210</v>
       </c>
       <c r="J7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="K7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M7" t="s">
         <v>71</v>
       </c>
       <c r="N7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O7" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P7" t="s">
-        <v>75</v>
+        <v>82</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>83</v>
+      </c>
+      <c r="R7" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:23">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -1004,43 +1073,49 @@
       <c r="H8">
         <v>40</v>
       </c>
-      <c r="I8" t="s">
-        <v>50</v>
+      <c r="I8">
+        <v>65</v>
       </c>
       <c r="J8" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="K8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="M8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N8" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="O8" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P8" t="s">
-        <v>75</v>
+        <v>82</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>83</v>
+      </c>
+      <c r="R8" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:23">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E9">
         <v>0.02</v>
@@ -1054,110 +1129,116 @@
       <c r="H9">
         <v>0.5</v>
       </c>
-      <c r="I9" t="s">
-        <v>51</v>
+      <c r="I9">
+        <v>0.8</v>
       </c>
       <c r="J9" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="K9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N9" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="O9" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P9" t="s">
-        <v>75</v>
+        <v>82</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>83</v>
+      </c>
+      <c r="R9" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:23">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="O10" t="s">
+        <v>81</v>
+      </c>
+      <c r="P10" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>83</v>
+      </c>
+      <c r="R10" t="s">
+        <v>84</v>
+      </c>
+      <c r="S10" t="s">
+        <v>85</v>
+      </c>
+      <c r="T10" t="s">
+        <v>87</v>
+      </c>
+      <c r="U10" t="s">
+        <v>88</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
         <v>44</v>
       </c>
-      <c r="M10" t="s">
-        <v>72</v>
-      </c>
-      <c r="N10" t="s">
-        <v>73</v>
-      </c>
-      <c r="O10" t="s">
-        <v>74</v>
-      </c>
-      <c r="P10" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>76</v>
-      </c>
-      <c r="R10" t="s">
-        <v>78</v>
-      </c>
-      <c r="S10" t="s">
-        <v>79</v>
-      </c>
-      <c r="T10">
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="O11" t="s">
+        <v>81</v>
+      </c>
+      <c r="P11" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>83</v>
+      </c>
+      <c r="R11" t="s">
+        <v>84</v>
+      </c>
+      <c r="S11" t="s">
+        <v>86</v>
+      </c>
+      <c r="T11" t="s">
+        <v>87</v>
+      </c>
+      <c r="U11" t="s">
+        <v>88</v>
+      </c>
+      <c r="V11">
         <v>0.2</v>
       </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21">
-      <c r="A11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" t="s">
-        <v>44</v>
-      </c>
-      <c r="M11" t="s">
-        <v>72</v>
-      </c>
-      <c r="N11" t="s">
-        <v>73</v>
-      </c>
-      <c r="O11" t="s">
-        <v>74</v>
-      </c>
-      <c r="P11" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>77</v>
-      </c>
-      <c r="R11" t="s">
-        <v>78</v>
-      </c>
-      <c r="S11" t="s">
-        <v>79</v>
-      </c>
-      <c r="T11">
-        <v>0.2</v>
-      </c>
-      <c r="U11" t="b">
+      <c r="W11" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_mapping_params.xlsx
+++ b/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_mapping_params.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="88">
   <si>
     <t>mapping_id</t>
   </si>
@@ -73,7 +73,7 @@
     <t>sensor_id</t>
   </si>
   <si>
-    <t>qfa_window</t>
+    <t>qha_window</t>
   </si>
   <si>
     <t>production_evidence</t>
@@ -106,13 +106,13 @@
     <t>Q_GS_gap_run_count</t>
   </si>
   <si>
-    <t>Q_FA_info_empty_cov</t>
-  </si>
-  <si>
-    <t>Q_FA_DO_1_4_process_floor</t>
-  </si>
-  <si>
-    <t>Q_FA_DO_2_4_process_floor</t>
+    <t>Q_HA_hard_stasis_fraction_observed</t>
+  </si>
+  <si>
+    <t>Q_HA_DO_1_4_process_floor</t>
+  </si>
+  <si>
+    <t>Q_HA_DO_2_4_process_floor</t>
   </si>
   <si>
     <t>Q_TI</t>
@@ -121,7 +121,7 @@
     <t>Q_GS</t>
   </si>
   <si>
-    <t>Q_FA</t>
+    <t>Q_HA</t>
   </si>
   <si>
     <t>missing_rate</t>
@@ -145,10 +145,7 @@
     <t>gap_run_count</t>
   </si>
   <si>
-    <t>info_empty_cov</t>
-  </si>
-  <si>
-    <t>qfa_unavailable</t>
+    <t>hard_stasis_fraction_observed</t>
   </si>
   <si>
     <t>piecewise_linear</t>
@@ -262,13 +259,13 @@
     <t>d2_sensors.yaml+d2_mapping.yaml</t>
   </si>
   <si>
-    <t>d2_v3_source_timestamp_qti_r1</t>
-  </si>
-  <si>
-    <t>NorthBank_D2_v3_20260804</t>
-  </si>
-  <si>
-    <t>2026-08-04</t>
+    <t>d2_v4_strict_hard_availability_r1</t>
+  </si>
+  <si>
+    <t>NorthBank_D2_v4_20260805</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
   </si>
   <si>
     <t>DO_1_4</t>
@@ -280,7 +277,7 @@
     <t>6h</t>
   </si>
   <si>
-    <t>missing,long_gap,hard_observed_stasis</t>
+    <t>present_raw_and_hard_observed_stasis</t>
   </si>
 </sst>
 </file>
@@ -723,7 +720,7 @@
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E2">
         <v>0.005</v>
@@ -741,31 +738,31 @@
         <v>0.25</v>
       </c>
       <c r="J2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P2" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q2" t="s">
         <v>82</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>83</v>
-      </c>
-      <c r="R2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -779,7 +776,7 @@
         <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E3">
         <v>0.001</v>
@@ -797,31 +794,31 @@
         <v>0.09</v>
       </c>
       <c r="J3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P3" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q3" t="s">
         <v>82</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>83</v>
-      </c>
-      <c r="R3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -835,7 +832,7 @@
         <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E4">
         <v>0.001</v>
@@ -853,31 +850,31 @@
         <v>0.09</v>
       </c>
       <c r="J4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P4" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q4" t="s">
         <v>82</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>83</v>
-      </c>
-      <c r="R4" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -891,7 +888,7 @@
         <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E5">
         <v>0.005</v>
@@ -909,31 +906,31 @@
         <v>0.15</v>
       </c>
       <c r="J5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P5" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q5" t="s">
         <v>82</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>83</v>
-      </c>
-      <c r="R5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -947,7 +944,7 @@
         <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -965,31 +962,31 @@
         <v>660</v>
       </c>
       <c r="J6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P6" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q6" t="s">
         <v>82</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>83</v>
-      </c>
-      <c r="R6" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -1003,7 +1000,7 @@
         <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -1021,31 +1018,31 @@
         <v>210</v>
       </c>
       <c r="J7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P7" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q7" t="s">
         <v>82</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>83</v>
-      </c>
-      <c r="R7" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -1059,7 +1056,7 @@
         <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -1077,31 +1074,31 @@
         <v>65</v>
       </c>
       <c r="J8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P8" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q8" t="s">
         <v>82</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>83</v>
-      </c>
-      <c r="R8" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:23">
@@ -1115,7 +1112,7 @@
         <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9">
         <v>0.02</v>
@@ -1133,31 +1130,31 @@
         <v>0.8</v>
       </c>
       <c r="J9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N9" t="s">
+        <v>78</v>
+      </c>
+      <c r="O9" t="s">
         <v>79</v>
       </c>
-      <c r="O9" t="s">
-        <v>80</v>
-      </c>
       <c r="P9" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q9" t="s">
         <v>82</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
         <v>83</v>
-      </c>
-      <c r="R9" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -1168,31 +1165,31 @@
         <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O10" t="s">
+        <v>80</v>
+      </c>
+      <c r="P10" t="s">
         <v>81</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
         <v>82</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>83</v>
       </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
         <v>84</v>
       </c>
-      <c r="S10" t="s">
-        <v>85</v>
-      </c>
       <c r="T10" t="s">
+        <v>86</v>
+      </c>
+      <c r="U10" t="s">
         <v>87</v>
-      </c>
-      <c r="U10" t="s">
-        <v>88</v>
       </c>
       <c r="V10">
         <v>0.2</v>
@@ -1209,31 +1206,31 @@
         <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O11" t="s">
+        <v>80</v>
+      </c>
+      <c r="P11" t="s">
         <v>81</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
         <v>82</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
         <v>83</v>
       </c>
-      <c r="R11" t="s">
-        <v>84</v>
-      </c>
       <c r="S11" t="s">
+        <v>85</v>
+      </c>
+      <c r="T11" t="s">
         <v>86</v>
       </c>
-      <c r="T11" t="s">
+      <c r="U11" t="s">
         <v>87</v>
-      </c>
-      <c r="U11" t="s">
-        <v>88</v>
       </c>
       <c r="V11">
         <v>0.2</v>
